--- a/artfynd/A 61137-2022 artfynd.xlsx
+++ b/artfynd/A 61137-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 61137-2022 artfynd.xlsx
+++ b/artfynd/A 61137-2022 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>89439317</v>
+        <v>89439313</v>
       </c>
       <c r="B2" t="n">
-        <v>95520</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106229</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>224362</v>
+        <v>221725</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Nordlummer</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum subsp. alpestre</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hartm.) Á. Löve &amp; D. Löve</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>660222.5677588462</v>
+        <v>660223</v>
       </c>
       <c r="R2" t="n">
-        <v>7316776.122720508</v>
+        <v>7316776</v>
       </c>
       <c r="S2" t="n">
         <v>30</v>
@@ -748,19 +743,9 @@
           <t>2020-07-09</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2020-07-09</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,50 +777,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>89439313</v>
+        <v>89439242</v>
       </c>
       <c r="B3" t="n">
-        <v>103250</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>105261</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221725</v>
+        <v>223989</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Sandsyra</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Rumex acetosella subsp. arenicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>Y. Mäkinen ex Elven</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Östansjövägen, Petterjaurvägen/krök Guollasjåhka syd S Nimtek-vägen, Pi lm</t>
+          <t>Östansjövägen, Petterjaurvägen/bäck mot Guollasjåhka, Pi lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>660222.5677588462</v>
+        <v>660112</v>
       </c>
       <c r="R3" t="n">
-        <v>7316776.122720508</v>
+        <v>7316654</v>
       </c>
       <c r="S3" t="n">
         <v>30</v>
@@ -865,19 +845,9 @@
           <t>2020-07-09</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2020-07-09</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -891,7 +861,17 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>myrartad jokkzon</t>
+          <t>bäckzon</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>Umeå-Herbarium UME</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>20-028</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -909,50 +889,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>89439242</v>
+        <v>89439317</v>
       </c>
       <c r="B4" t="n">
-        <v>102304</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97984</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>223989</v>
+        <v>224362</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sandsyra</t>
+          <t>Nordlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rumex acetosella subsp. arenicola</t>
+          <t>Lycopodium annotinum subsp. alpestre</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Y. Mäkinen ex Elven</t>
+          <t>(Hartm.) Á. Löve &amp; D. Löve</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Östansjövägen, Petterjaurvägen/bäck mot Guollasjåhka, Pi lm</t>
+          <t>Östansjövägen, Petterjaurvägen/krök Guollasjåhka syd S Nimtek-vägen, Pi lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>660112.301030701</v>
+        <v>660223</v>
       </c>
       <c r="R4" t="n">
-        <v>7316653.7349518</v>
+        <v>7316776</v>
       </c>
       <c r="S4" t="n">
         <v>30</v>
@@ -982,19 +957,9 @@
           <t>2020-07-09</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2020-07-09</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1008,17 +973,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>bäckzon</t>
-        </is>
-      </c>
-      <c r="AP4" t="inlineStr">
-        <is>
-          <t>Pite lappmarks flora – herbarium FPLF</t>
-        </is>
-      </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>20-028</t>
+          <t>myrartad jokkzon</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>

--- a/artfynd/A 61137-2022 artfynd.xlsx
+++ b/artfynd/A 61137-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89439313</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89439242</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -988,8 +1003,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89439317</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>